--- a/Unity/Assets/Config/Excel/Skill/ElementReactionConfig.xlsx
+++ b/Unity/Assets/Config/Excel/Skill/ElementReactionConfig.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="89">
   <si>
     <t>Id</t>
   </si>
@@ -25,27 +25,27 @@
     <t>目标元素</t>
   </si>
   <si>
-    <t>反应结果</t>
-  </si>
-  <si>
-    <t>伤害加成</t>
-  </si>
-  <si>
-    <t>反应后残留的元素，0表示清除</t>
-  </si>
-  <si>
-    <t>消耗目标元素量(%)</t>
+    <t>反应结果，火烧木头为例，产生结果是持续燃烧，直到木头烧完。结果会挂在材质表面。</t>
+  </si>
+  <si>
+    <t>伤害放大系数，只针对元素伤害放大, &gt; 1 为放大， &lt; 1 为减少伤害。</t>
+  </si>
+  <si>
+    <t>反应强度，0不发生反应， 一般Intensity 设置1。 攻击者不消耗元素量，反应结果是, 被攻击者元素销量 和产生的伤害都是 Min(攻击者元素量 * Intensity, 被攻击者元素销量)</t>
+  </si>
+  <si>
+    <t>反应后剩余元素每秒消耗量, 0不消耗。比如火点燃了木头，后续持续消耗剩余的木头。</t>
+  </si>
+  <si>
+    <t>反应后附加元素的持续时间，单位毫秒。如果一直燃烧，直到结束，设置一个较大值。</t>
+  </si>
+  <si>
+    <t>反应后附加的BUFF，比如持续伤害，持续周边AOE，持续蔓延。</t>
   </si>
   <si>
     <t>VFX效果名称</t>
   </si>
   <si>
-    <t>是否完全消耗目标</t>
-  </si>
-  <si>
-    <t>目标施加BuffID列表</t>
-  </si>
-  <si>
     <t>Description</t>
   </si>
   <si>
@@ -61,21 +61,21 @@
     <t>DamageMultiplier</t>
   </si>
   <si>
-    <t>RemainElement</t>
-  </si>
-  <si>
-    <t>GaugeConsumption</t>
+    <t>Intensity</t>
+  </si>
+  <si>
+    <t>DaceyPerSecond</t>
+  </si>
+  <si>
+    <t>Duration</t>
+  </si>
+  <si>
+    <t>ApplyBuffs</t>
   </si>
   <si>
     <t>VfxName</t>
   </si>
   <si>
-    <t>IsConsumed</t>
-  </si>
-  <si>
-    <t>ApplyBuffs</t>
-  </si>
-  <si>
     <t>int</t>
   </si>
   <si>
@@ -91,6 +91,18 @@
     <t>火+水=蒸发(高伤，水消失)</t>
   </si>
   <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>3000</t>
+  </si>
+  <si>
+    <t>1001</t>
+  </si>
+  <si>
     <t>Vfx_Vaporize</t>
   </si>
   <si>
@@ -103,6 +115,9 @@
     <t>火+冰=融化，冰化成水</t>
   </si>
   <si>
+    <t>1002</t>
+  </si>
+  <si>
     <t>Vfx_Melt</t>
   </si>
   <si>
@@ -115,18 +130,27 @@
     <t>雷+冰=超导(降低防御)</t>
   </si>
   <si>
+    <t>0</t>
+  </si>
+  <si>
     <t>Vfx_Superconduct</t>
   </si>
   <si>
     <t>风+火=扩散</t>
   </si>
   <si>
+    <t>1003</t>
+  </si>
+  <si>
     <t>Vfx_Swirl_Fire</t>
   </si>
   <si>
     <t>火+草/油=燃烧</t>
   </si>
   <si>
+    <t>1004</t>
+  </si>
+  <si>
     <t>Vfx_Burning</t>
   </si>
   <si>
@@ -139,6 +163,9 @@
     <t>冰+水=冻结</t>
   </si>
   <si>
+    <t>1005</t>
+  </si>
+  <si>
     <t>Vfx_Frozen</t>
   </si>
   <si>
@@ -157,30 +184,45 @@
     <t>风+冰=扩散</t>
   </si>
   <si>
+    <t>1006</t>
+  </si>
+  <si>
     <t>Vfx_Swirl_Ice</t>
   </si>
   <si>
     <t>风+雷=扩散</t>
   </si>
   <si>
+    <t>1007</t>
+  </si>
+  <si>
     <t>Vfx_Swirl_Elec</t>
   </si>
   <si>
     <t>岩+火=结晶</t>
   </si>
   <si>
+    <t>1008</t>
+  </si>
+  <si>
     <t>Vfx_Crystallize_Fire</t>
   </si>
   <si>
     <t>岩+水=结晶</t>
   </si>
   <si>
+    <t>1009</t>
+  </si>
+  <si>
     <t>Vfx_Crystallize_Water</t>
   </si>
   <si>
     <t>岩+雷=结晶</t>
   </si>
   <si>
+    <t>1010</t>
+  </si>
+  <si>
     <t>Vfx_Crystallize_Elec</t>
   </si>
   <si>
@@ -202,7 +244,13 @@
     <t>水+冰=冻结</t>
   </si>
   <si>
+    <t>1011</t>
+  </si>
+  <si>
     <t>冰+雷=超导</t>
+  </si>
+  <si>
+    <t>1012</t>
   </si>
   <si>
     <t>雷+火=超载</t>
@@ -262,7 +310,7 @@
       <name val="Helvetica Neue"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -271,12 +319,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="10"/>
+        <fgColor indexed="9"/>
+        <bgColor auto="1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="12"/>
+        <bgColor auto="1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="13"/>
         <bgColor auto="1"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -286,16 +346,151 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </left>
       <right style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </right>
       <top style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </top>
       <bottom style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="10"/>
+      </left>
+      <right style="thin">
+        <color indexed="11"/>
+      </right>
+      <top style="thin">
+        <color indexed="10"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="10"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="11"/>
+      </left>
+      <right style="thin">
+        <color indexed="11"/>
+      </right>
+      <top style="thin">
+        <color indexed="11"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="11"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="11"/>
+      </left>
+      <right style="thin">
+        <color indexed="10"/>
+      </right>
+      <top style="thin">
+        <color indexed="10"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="10"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="10"/>
+      </left>
+      <right style="thin">
+        <color indexed="10"/>
+      </right>
+      <top style="thin">
+        <color indexed="10"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="11"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="10"/>
+      </left>
+      <right style="thin">
+        <color indexed="11"/>
+      </right>
+      <top style="thin">
+        <color indexed="10"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="11"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="11"/>
+      </left>
+      <right style="thin">
+        <color indexed="10"/>
+      </right>
+      <top style="thin">
+        <color indexed="10"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="11"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="10"/>
+      </left>
+      <right style="thin">
+        <color indexed="10"/>
+      </right>
+      <top style="thin">
+        <color indexed="11"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="10"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="10"/>
+      </left>
+      <right style="thin">
+        <color indexed="11"/>
+      </right>
+      <top style="thin">
+        <color indexed="11"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="10"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="11"/>
+      </left>
+      <right style="thin">
+        <color indexed="10"/>
+      </right>
+      <top style="thin">
+        <color indexed="11"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="10"/>
       </bottom>
       <diagonal/>
     </border>
@@ -305,26 +500,71 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="0" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -344,8 +584,11 @@
       <rgbColor rgb="ffff00ff"/>
       <rgbColor rgb="ff00ffff"/>
       <rgbColor rgb="ff000000"/>
+      <rgbColor rgb="ffffffff"/>
       <rgbColor rgb="ffdddddd"/>
+      <rgbColor rgb="ffa5a5a5"/>
       <rgbColor rgb="ff88e168"/>
+      <rgbColor rgb="ff61d836"/>
     </indexedColors>
   </colors>
 </styleSheet>
@@ -1384,8 +1627,8 @@
   <sheetFormatPr defaultColWidth="8.33333" defaultRowHeight="19.9" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="2" width="8.35156" style="1" customWidth="1"/>
-    <col min="3" max="3" width="3.35156" style="1" customWidth="1"/>
-    <col min="4" max="4" width="27.6719" style="1" customWidth="1"/>
+    <col min="3" max="3" width="5.35156" style="1" customWidth="1"/>
+    <col min="4" max="4" width="27.3516" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.3516" style="1" customWidth="1"/>
     <col min="6" max="6" width="9.35156" style="1" customWidth="1"/>
     <col min="7" max="7" width="8.17188" style="1" customWidth="1"/>
@@ -1406,1241 +1649,1247 @@
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="5"/>
     </row>
     <row r="2" ht="20.25" customHeight="1">
       <c r="A2" s="2"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="10"/>
     </row>
     <row r="3" ht="20.05" customHeight="1">
       <c r="A3" s="2"/>
-      <c r="B3" s="3"/>
-      <c r="C3" t="s" s="4">
+      <c r="B3" s="6"/>
+      <c r="C3" t="s" s="11">
         <v>0</v>
       </c>
-      <c r="D3" t="s" s="4">
+      <c r="D3" t="s" s="11">
         <v>1</v>
       </c>
-      <c r="E3" t="s" s="4">
+      <c r="E3" t="s" s="11">
         <v>2</v>
       </c>
-      <c r="F3" t="s" s="4">
+      <c r="F3" t="s" s="12">
         <v>3</v>
       </c>
-      <c r="G3" t="s" s="4">
+      <c r="G3" t="s" s="13">
         <v>4</v>
       </c>
-      <c r="H3" t="s" s="4">
+      <c r="H3" t="s" s="13">
         <v>5</v>
       </c>
-      <c r="I3" t="s" s="4">
+      <c r="I3" t="s" s="13">
         <v>6</v>
       </c>
-      <c r="J3" t="s" s="4">
+      <c r="J3" t="s" s="13">
         <v>7</v>
       </c>
-      <c r="K3" t="s" s="4">
+      <c r="K3" t="s" s="13">
         <v>8</v>
       </c>
-      <c r="L3" t="s" s="4">
+      <c r="L3" t="s" s="13">
         <v>9</v>
       </c>
-      <c r="M3" t="s" s="4">
+      <c r="M3" t="s" s="13">
         <v>10</v>
       </c>
     </row>
     <row r="4" ht="20.05" customHeight="1">
       <c r="A4" s="2"/>
-      <c r="B4" s="3"/>
-      <c r="C4" t="s" s="4">
+      <c r="B4" s="6"/>
+      <c r="C4" t="s" s="11">
         <v>0</v>
       </c>
-      <c r="D4" t="s" s="4">
+      <c r="D4" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="E4" t="s" s="4">
+      <c r="E4" t="s" s="11">
         <v>12</v>
       </c>
-      <c r="F4" t="s" s="4">
+      <c r="F4" t="s" s="11">
         <v>13</v>
       </c>
-      <c r="G4" t="s" s="4">
+      <c r="G4" t="s" s="14">
         <v>14</v>
       </c>
-      <c r="H4" t="s" s="4">
+      <c r="H4" t="s" s="15">
         <v>15</v>
       </c>
-      <c r="I4" t="s" s="4">
+      <c r="I4" t="s" s="13">
         <v>16</v>
       </c>
-      <c r="J4" t="s" s="4">
+      <c r="J4" t="s" s="13">
         <v>17</v>
       </c>
-      <c r="K4" t="s" s="4">
+      <c r="K4" t="s" s="13">
         <v>18</v>
       </c>
-      <c r="L4" t="s" s="4">
+      <c r="L4" t="s" s="13">
         <v>19</v>
       </c>
-      <c r="M4" t="s" s="4">
+      <c r="M4" t="s" s="16">
         <v>20</v>
       </c>
     </row>
     <row r="5" ht="20.05" customHeight="1">
       <c r="A5" s="2"/>
-      <c r="B5" s="3"/>
-      <c r="C5" t="s" s="4">
+      <c r="B5" s="6"/>
+      <c r="C5" t="s" s="11">
         <v>21</v>
       </c>
-      <c r="D5" t="s" s="4">
+      <c r="D5" t="s" s="11">
         <v>22</v>
       </c>
-      <c r="E5" t="s" s="4">
+      <c r="E5" t="s" s="11">
         <v>21</v>
       </c>
-      <c r="F5" t="s" s="4">
+      <c r="F5" t="s" s="11">
         <v>21</v>
       </c>
-      <c r="G5" t="s" s="4">
+      <c r="G5" t="s" s="11">
         <v>21</v>
       </c>
-      <c r="H5" t="s" s="4">
+      <c r="H5" t="s" s="12">
         <v>23</v>
       </c>
-      <c r="I5" t="s" s="4">
+      <c r="I5" t="s" s="13">
+        <v>23</v>
+      </c>
+      <c r="J5" t="s" s="13">
         <v>21</v>
       </c>
-      <c r="J5" t="s" s="4">
-        <v>23</v>
-      </c>
-      <c r="K5" t="s" s="4">
+      <c r="K5" t="s" s="13">
+        <v>21</v>
+      </c>
+      <c r="L5" t="s" s="13">
+        <v>24</v>
+      </c>
+      <c r="M5" t="s" s="17">
         <v>22</v>
-      </c>
-      <c r="L5" t="s" s="4">
-        <v>21</v>
-      </c>
-      <c r="M5" t="s" s="4">
-        <v>24</v>
       </c>
     </row>
     <row r="6" ht="20.05" customHeight="1">
       <c r="A6" s="2"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="5">
+      <c r="B6" s="6"/>
+      <c r="C6" s="18">
         <v>1</v>
       </c>
-      <c r="D6" t="s" s="6">
+      <c r="D6" t="s" s="19">
         <v>25</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="18">
         <v>1</v>
       </c>
-      <c r="F6" s="5">
+      <c r="F6" s="18">
         <v>2</v>
       </c>
-      <c r="G6" s="5">
+      <c r="G6" s="18">
         <v>1</v>
       </c>
-      <c r="H6" s="5">
+      <c r="H6" s="20">
         <v>2</v>
       </c>
-      <c r="I6" s="5">
-        <v>0</v>
-      </c>
-      <c r="J6" s="5">
-        <v>100</v>
-      </c>
-      <c r="K6" t="s" s="6">
-        <v>26</v>
-      </c>
-      <c r="L6" s="5">
-        <v>1</v>
-      </c>
-      <c r="M6" s="5">
-        <v>123</v>
+      <c r="I6" t="s" s="9">
+        <v>26</v>
+      </c>
+      <c r="J6" t="s" s="9">
+        <v>27</v>
+      </c>
+      <c r="K6" t="s" s="9">
+        <v>28</v>
+      </c>
+      <c r="L6" t="s" s="9">
+        <v>29</v>
+      </c>
+      <c r="M6" t="s" s="21">
+        <v>30</v>
       </c>
     </row>
     <row r="7" ht="20.05" customHeight="1">
       <c r="A7" s="2"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="5">
+      <c r="B7" s="6"/>
+      <c r="C7" s="18">
         <v>2</v>
       </c>
-      <c r="D7" t="s" s="6">
-        <v>27</v>
-      </c>
-      <c r="E7" s="5">
+      <c r="D7" t="s" s="19">
+        <v>31</v>
+      </c>
+      <c r="E7" s="18">
         <v>2</v>
       </c>
-      <c r="F7" s="5">
+      <c r="F7" s="18">
         <v>1</v>
       </c>
-      <c r="G7" s="5">
+      <c r="G7" s="18">
         <v>1</v>
       </c>
-      <c r="H7" s="5">
+      <c r="H7" s="20">
         <v>1.5</v>
       </c>
-      <c r="I7" s="5">
-        <v>0</v>
-      </c>
-      <c r="J7" s="5">
-        <v>100</v>
-      </c>
-      <c r="K7" t="s" s="6">
-        <v>28</v>
-      </c>
-      <c r="L7" s="5">
-        <v>1</v>
-      </c>
-      <c r="M7" s="5">
-        <v>111</v>
+      <c r="I7" t="s" s="9">
+        <v>26</v>
+      </c>
+      <c r="J7" t="s" s="9">
+        <v>27</v>
+      </c>
+      <c r="K7" t="s" s="9">
+        <v>28</v>
+      </c>
+      <c r="L7" t="s" s="9">
+        <v>29</v>
+      </c>
+      <c r="M7" t="s" s="21">
+        <v>32</v>
       </c>
     </row>
     <row r="8" ht="20.05" customHeight="1">
       <c r="A8" s="2"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="5">
+      <c r="B8" s="6"/>
+      <c r="C8" s="18">
         <v>3</v>
       </c>
-      <c r="D8" t="s" s="6">
-        <v>29</v>
-      </c>
-      <c r="E8" s="5">
+      <c r="D8" t="s" s="19">
+        <v>33</v>
+      </c>
+      <c r="E8" s="18">
         <v>1</v>
       </c>
-      <c r="F8" s="5">
+      <c r="F8" s="18">
         <v>3</v>
       </c>
-      <c r="G8" s="5">
+      <c r="G8" s="18">
         <v>2</v>
       </c>
-      <c r="H8" s="5">
+      <c r="H8" s="20">
         <v>1.5</v>
       </c>
-      <c r="I8" s="5">
-        <v>2</v>
-      </c>
-      <c r="J8" s="5">
-        <v>100</v>
-      </c>
-      <c r="K8" t="s" s="6">
-        <v>30</v>
-      </c>
-      <c r="L8" s="5">
-        <v>1</v>
-      </c>
-      <c r="M8" s="5">
-        <v>12</v>
+      <c r="I8" t="s" s="9">
+        <v>26</v>
+      </c>
+      <c r="J8" t="s" s="9">
+        <v>27</v>
+      </c>
+      <c r="K8" t="s" s="9">
+        <v>28</v>
+      </c>
+      <c r="L8" t="s" s="9">
+        <v>34</v>
+      </c>
+      <c r="M8" t="s" s="21">
+        <v>35</v>
       </c>
     </row>
     <row r="9" ht="20.05" customHeight="1">
       <c r="A9" s="2"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="5">
+      <c r="B9" s="6"/>
+      <c r="C9" s="18">
         <v>4</v>
       </c>
-      <c r="D9" t="s" s="6">
-        <v>31</v>
-      </c>
-      <c r="E9" s="5">
+      <c r="D9" t="s" s="19">
+        <v>36</v>
+      </c>
+      <c r="E9" s="18">
         <v>4</v>
       </c>
-      <c r="F9" s="5">
+      <c r="F9" s="18">
         <v>2</v>
       </c>
-      <c r="G9" s="5">
+      <c r="G9" s="18">
         <v>5</v>
       </c>
-      <c r="H9" s="5">
+      <c r="H9" s="20">
         <v>1.2</v>
       </c>
-      <c r="I9" s="5">
-        <v>2</v>
-      </c>
-      <c r="J9" s="5">
-        <v>40</v>
-      </c>
-      <c r="K9" t="s" s="6">
-        <v>32</v>
-      </c>
-      <c r="L9" s="5">
-        <v>0</v>
-      </c>
-      <c r="M9" s="5">
-        <v>333</v>
+      <c r="I9" t="s" s="9">
+        <v>26</v>
+      </c>
+      <c r="J9" t="s" s="9">
+        <v>27</v>
+      </c>
+      <c r="K9" t="s" s="9">
+        <v>28</v>
+      </c>
+      <c r="L9" t="s" s="9">
+        <v>34</v>
+      </c>
+      <c r="M9" t="s" s="21">
+        <v>37</v>
       </c>
     </row>
     <row r="10" ht="20.05" customHeight="1">
       <c r="A10" s="2"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="5">
+      <c r="B10" s="6"/>
+      <c r="C10" s="18">
         <v>5</v>
       </c>
-      <c r="D10" t="s" s="6">
-        <v>33</v>
-      </c>
-      <c r="E10" s="5">
+      <c r="D10" t="s" s="19">
+        <v>38</v>
+      </c>
+      <c r="E10" s="18">
         <v>4</v>
       </c>
-      <c r="F10" s="5">
+      <c r="F10" s="18">
         <v>3</v>
       </c>
-      <c r="G10" s="5">
+      <c r="G10" s="18">
         <v>4</v>
       </c>
-      <c r="H10" s="5">
+      <c r="H10" s="20">
         <v>2</v>
       </c>
-      <c r="I10" s="5">
-        <v>3</v>
-      </c>
-      <c r="J10" s="5">
-        <v>0</v>
-      </c>
-      <c r="K10" t="s" s="6">
-        <v>34</v>
-      </c>
-      <c r="L10" s="5">
-        <v>0</v>
-      </c>
-      <c r="M10" s="5">
-        <v>555</v>
+      <c r="I10" t="s" s="9">
+        <v>26</v>
+      </c>
+      <c r="J10" t="s" s="9">
+        <v>27</v>
+      </c>
+      <c r="K10" t="s" s="9">
+        <v>28</v>
+      </c>
+      <c r="L10" t="s" s="9">
+        <v>39</v>
+      </c>
+      <c r="M10" t="s" s="21">
+        <v>40</v>
       </c>
     </row>
     <row r="11" ht="20.05" customHeight="1">
       <c r="A11" s="2"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="5">
+      <c r="B11" s="6"/>
+      <c r="C11" s="18">
         <v>6</v>
       </c>
-      <c r="D11" t="s" s="6">
-        <v>35</v>
-      </c>
-      <c r="E11" s="5">
+      <c r="D11" t="s" s="19">
+        <v>41</v>
+      </c>
+      <c r="E11" s="18">
         <v>5</v>
       </c>
-      <c r="F11" s="5">
+      <c r="F11" s="18">
         <v>1</v>
       </c>
-      <c r="G11" s="5">
+      <c r="G11" s="18">
         <v>8</v>
       </c>
-      <c r="H11" s="5">
+      <c r="H11" s="20">
         <v>1.3</v>
       </c>
-      <c r="I11" s="5">
-        <v>5</v>
-      </c>
-      <c r="J11" s="5">
-        <v>50</v>
-      </c>
-      <c r="K11" t="s" s="6">
-        <v>36</v>
-      </c>
-      <c r="L11" s="5">
-        <v>0</v>
-      </c>
-      <c r="M11" s="5">
-        <v>1006</v>
+      <c r="I11" t="s" s="9">
+        <v>26</v>
+      </c>
+      <c r="J11" t="s" s="9">
+        <v>27</v>
+      </c>
+      <c r="K11" t="s" s="9">
+        <v>28</v>
+      </c>
+      <c r="L11" t="s" s="9">
+        <v>42</v>
+      </c>
+      <c r="M11" t="s" s="21">
+        <v>43</v>
       </c>
     </row>
     <row r="12" ht="20.05" customHeight="1">
       <c r="A12" s="2"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="5">
+      <c r="B12" s="6"/>
+      <c r="C12" s="18">
         <v>7</v>
       </c>
-      <c r="D12" t="s" s="6">
-        <v>37</v>
-      </c>
-      <c r="E12" s="5">
+      <c r="D12" t="s" s="19">
+        <v>44</v>
+      </c>
+      <c r="E12" s="18">
         <v>1</v>
       </c>
-      <c r="F12" s="5">
+      <c r="F12" s="18">
         <v>0</v>
       </c>
-      <c r="G12" s="5">
+      <c r="G12" s="18">
         <v>10</v>
       </c>
-      <c r="H12" s="5">
+      <c r="H12" s="20">
         <v>1</v>
       </c>
-      <c r="I12" s="5">
-        <v>1</v>
-      </c>
-      <c r="J12" s="5">
-        <v>0</v>
-      </c>
-      <c r="K12" t="s" s="6">
-        <v>38</v>
-      </c>
-      <c r="L12" s="5">
-        <v>0</v>
-      </c>
-      <c r="M12" s="5">
-        <v>1001</v>
+      <c r="I12" t="s" s="9">
+        <v>26</v>
+      </c>
+      <c r="J12" t="s" s="9">
+        <v>27</v>
+      </c>
+      <c r="K12" t="s" s="9">
+        <v>28</v>
+      </c>
+      <c r="L12" t="s" s="9">
+        <v>45</v>
+      </c>
+      <c r="M12" t="s" s="21">
+        <v>46</v>
       </c>
     </row>
     <row r="13" ht="20.05" customHeight="1">
       <c r="A13" s="2"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="5">
+      <c r="B13" s="6"/>
+      <c r="C13" s="18">
         <v>8</v>
       </c>
-      <c r="D13" t="s" s="6">
-        <v>39</v>
-      </c>
-      <c r="E13" s="5">
+      <c r="D13" t="s" s="19">
+        <v>47</v>
+      </c>
+      <c r="E13" s="18">
         <v>1</v>
       </c>
-      <c r="F13" s="5">
+      <c r="F13" s="18">
         <v>4</v>
       </c>
-      <c r="G13" s="5">
+      <c r="G13" s="18">
         <v>3</v>
       </c>
-      <c r="H13" s="5">
+      <c r="H13" s="20">
         <v>2.5</v>
       </c>
-      <c r="I13" s="5">
-        <v>0</v>
-      </c>
-      <c r="J13" s="5">
-        <v>100</v>
-      </c>
-      <c r="K13" t="s" s="6">
-        <v>40</v>
-      </c>
-      <c r="L13" s="5">
-        <v>1</v>
-      </c>
-      <c r="M13" s="5">
-        <v>1013</v>
+      <c r="I13" t="s" s="9">
+        <v>26</v>
+      </c>
+      <c r="J13" t="s" s="9">
+        <v>27</v>
+      </c>
+      <c r="K13" t="s" s="9">
+        <v>28</v>
+      </c>
+      <c r="L13" t="s" s="9">
+        <v>45</v>
+      </c>
+      <c r="M13" t="s" s="21">
+        <v>48</v>
       </c>
     </row>
     <row r="14" ht="20.05" customHeight="1">
       <c r="A14" s="2"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="5">
+      <c r="B14" s="6"/>
+      <c r="C14" s="18">
         <v>9</v>
       </c>
-      <c r="D14" t="s" s="6">
-        <v>41</v>
-      </c>
-      <c r="E14" s="5">
+      <c r="D14" t="s" s="19">
+        <v>49</v>
+      </c>
+      <c r="E14" s="18">
         <v>3</v>
       </c>
-      <c r="F14" s="5">
+      <c r="F14" s="18">
         <v>2</v>
       </c>
-      <c r="G14" s="5">
+      <c r="G14" s="18">
         <v>6</v>
       </c>
-      <c r="H14" s="5">
+      <c r="H14" s="20">
         <v>1</v>
       </c>
-      <c r="I14" s="5">
-        <v>3</v>
-      </c>
-      <c r="J14" s="5">
-        <v>100</v>
-      </c>
-      <c r="K14" t="s" s="6">
-        <v>42</v>
-      </c>
-      <c r="L14" s="5">
-        <v>1</v>
-      </c>
-      <c r="M14" s="5">
-        <v>1005</v>
+      <c r="I14" t="s" s="9">
+        <v>26</v>
+      </c>
+      <c r="J14" t="s" s="9">
+        <v>27</v>
+      </c>
+      <c r="K14" t="s" s="9">
+        <v>28</v>
+      </c>
+      <c r="L14" t="s" s="9">
+        <v>50</v>
+      </c>
+      <c r="M14" t="s" s="21">
+        <v>51</v>
       </c>
     </row>
     <row r="15" ht="20.05" customHeight="1">
       <c r="A15" s="2"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="5">
+      <c r="B15" s="6"/>
+      <c r="C15" s="18">
         <v>10</v>
       </c>
-      <c r="D15" t="s" s="6">
-        <v>43</v>
-      </c>
-      <c r="E15" s="5">
+      <c r="D15" t="s" s="19">
+        <v>52</v>
+      </c>
+      <c r="E15" s="18">
         <v>6</v>
       </c>
-      <c r="F15" s="5">
+      <c r="F15" s="18">
         <v>0</v>
       </c>
-      <c r="G15" s="5">
+      <c r="G15" s="18">
         <v>7</v>
       </c>
-      <c r="H15" s="5">
+      <c r="H15" s="20">
         <v>3</v>
       </c>
-      <c r="I15" s="5">
-        <v>0</v>
-      </c>
-      <c r="J15" s="5">
-        <v>100</v>
-      </c>
-      <c r="K15" t="s" s="6">
-        <v>44</v>
-      </c>
-      <c r="L15" s="5">
-        <v>1</v>
-      </c>
-      <c r="M15" s="3"/>
+      <c r="I15" t="s" s="9">
+        <v>26</v>
+      </c>
+      <c r="J15" t="s" s="9">
+        <v>27</v>
+      </c>
+      <c r="K15" t="s" s="9">
+        <v>28</v>
+      </c>
+      <c r="L15" t="s" s="9">
+        <v>50</v>
+      </c>
+      <c r="M15" t="s" s="21">
+        <v>53</v>
+      </c>
     </row>
     <row r="16" ht="20.05" customHeight="1">
       <c r="A16" s="2"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="5">
+      <c r="B16" s="6"/>
+      <c r="C16" s="18">
         <v>11</v>
       </c>
-      <c r="D16" t="s" s="6">
-        <v>45</v>
-      </c>
-      <c r="E16" s="5">
+      <c r="D16" t="s" s="19">
+        <v>54</v>
+      </c>
+      <c r="E16" s="18">
         <v>5</v>
       </c>
-      <c r="F16" s="5">
+      <c r="F16" s="18">
         <v>2</v>
       </c>
-      <c r="G16" s="5">
+      <c r="G16" s="18">
         <v>8</v>
       </c>
-      <c r="H16" s="5">
+      <c r="H16" s="20">
         <v>1.2</v>
       </c>
-      <c r="I16" s="5">
-        <v>5</v>
-      </c>
-      <c r="J16" s="5">
-        <v>45</v>
-      </c>
-      <c r="K16" t="s" s="6">
-        <v>46</v>
-      </c>
-      <c r="L16" s="5">
-        <v>0</v>
-      </c>
-      <c r="M16" s="5">
-        <v>1007</v>
+      <c r="I16" t="s" s="9">
+        <v>26</v>
+      </c>
+      <c r="J16" t="s" s="9">
+        <v>27</v>
+      </c>
+      <c r="K16" t="s" s="9">
+        <v>28</v>
+      </c>
+      <c r="L16" t="s" s="9">
+        <v>39</v>
+      </c>
+      <c r="M16" t="s" s="21">
+        <v>55</v>
       </c>
     </row>
     <row r="17" ht="20.05" customHeight="1">
       <c r="A17" s="2"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="5">
+      <c r="B17" s="6"/>
+      <c r="C17" s="18">
         <v>12</v>
       </c>
-      <c r="D17" t="s" s="6">
-        <v>47</v>
-      </c>
-      <c r="E17" s="5">
+      <c r="D17" t="s" s="19">
+        <v>56</v>
+      </c>
+      <c r="E17" s="18">
         <v>5</v>
       </c>
-      <c r="F17" s="5">
+      <c r="F17" s="18">
         <v>3</v>
       </c>
-      <c r="G17" s="5">
+      <c r="G17" s="18">
         <v>8</v>
       </c>
-      <c r="H17" s="5">
+      <c r="H17" s="20">
         <v>1.4</v>
       </c>
-      <c r="I17" s="5">
-        <v>5</v>
-      </c>
-      <c r="J17" s="5">
-        <v>48</v>
-      </c>
-      <c r="K17" t="s" s="6">
-        <v>48</v>
-      </c>
-      <c r="L17" s="5">
-        <v>0</v>
-      </c>
-      <c r="M17" s="5">
-        <v>1008</v>
+      <c r="I17" t="s" s="9">
+        <v>26</v>
+      </c>
+      <c r="J17" t="s" s="9">
+        <v>27</v>
+      </c>
+      <c r="K17" t="s" s="9">
+        <v>28</v>
+      </c>
+      <c r="L17" t="s" s="9">
+        <v>57</v>
+      </c>
+      <c r="M17" t="s" s="21">
+        <v>58</v>
       </c>
     </row>
     <row r="18" ht="20.05" customHeight="1">
       <c r="A18" s="2"/>
-      <c r="B18" s="3"/>
-      <c r="C18" s="5">
+      <c r="B18" s="6"/>
+      <c r="C18" s="18">
         <v>13</v>
       </c>
-      <c r="D18" t="s" s="6">
-        <v>49</v>
-      </c>
-      <c r="E18" s="5">
+      <c r="D18" t="s" s="19">
+        <v>59</v>
+      </c>
+      <c r="E18" s="18">
         <v>5</v>
       </c>
-      <c r="F18" s="5">
+      <c r="F18" s="18">
         <v>4</v>
       </c>
-      <c r="G18" s="5">
+      <c r="G18" s="18">
         <v>8</v>
       </c>
-      <c r="H18" s="5">
+      <c r="H18" s="20">
         <v>1.6</v>
       </c>
-      <c r="I18" s="5">
-        <v>5</v>
-      </c>
-      <c r="J18" s="5">
-        <v>52</v>
-      </c>
-      <c r="K18" t="s" s="6">
-        <v>50</v>
-      </c>
-      <c r="L18" s="5">
-        <v>0</v>
-      </c>
-      <c r="M18" s="5">
-        <v>1009</v>
+      <c r="I18" t="s" s="9">
+        <v>26</v>
+      </c>
+      <c r="J18" t="s" s="9">
+        <v>27</v>
+      </c>
+      <c r="K18" t="s" s="9">
+        <v>28</v>
+      </c>
+      <c r="L18" t="s" s="9">
+        <v>60</v>
+      </c>
+      <c r="M18" t="s" s="21">
+        <v>61</v>
       </c>
     </row>
     <row r="19" ht="20.05" customHeight="1">
       <c r="A19" s="2"/>
-      <c r="B19" s="3"/>
-      <c r="C19" s="5">
+      <c r="B19" s="6"/>
+      <c r="C19" s="18">
         <v>14</v>
       </c>
-      <c r="D19" t="s" s="6">
-        <v>51</v>
-      </c>
-      <c r="E19" s="5">
+      <c r="D19" t="s" s="19">
+        <v>62</v>
+      </c>
+      <c r="E19" s="18">
         <v>6</v>
       </c>
-      <c r="F19" s="5">
+      <c r="F19" s="18">
         <v>1</v>
       </c>
-      <c r="G19" s="5">
+      <c r="G19" s="18">
         <v>9</v>
       </c>
-      <c r="H19" s="5">
+      <c r="H19" s="20">
         <v>1.2</v>
       </c>
-      <c r="I19" s="5">
-        <v>6</v>
-      </c>
-      <c r="J19" s="5">
-        <v>60</v>
-      </c>
-      <c r="K19" t="s" s="6">
-        <v>52</v>
-      </c>
-      <c r="L19" s="5">
-        <v>0</v>
-      </c>
-      <c r="M19" s="5">
-        <v>1010</v>
+      <c r="I19" t="s" s="9">
+        <v>26</v>
+      </c>
+      <c r="J19" t="s" s="9">
+        <v>27</v>
+      </c>
+      <c r="K19" t="s" s="9">
+        <v>28</v>
+      </c>
+      <c r="L19" t="s" s="9">
+        <v>63</v>
+      </c>
+      <c r="M19" t="s" s="21">
+        <v>64</v>
       </c>
     </row>
     <row r="20" ht="20.05" customHeight="1">
       <c r="A20" s="2"/>
-      <c r="B20" s="3"/>
-      <c r="C20" s="5">
+      <c r="B20" s="6"/>
+      <c r="C20" s="18">
         <v>15</v>
       </c>
-      <c r="D20" t="s" s="6">
-        <v>53</v>
-      </c>
-      <c r="E20" s="5">
+      <c r="D20" t="s" s="19">
+        <v>65</v>
+      </c>
+      <c r="E20" s="18">
         <v>6</v>
       </c>
-      <c r="F20" s="5">
+      <c r="F20" s="18">
         <v>2</v>
       </c>
-      <c r="G20" s="5">
+      <c r="G20" s="18">
         <v>9</v>
       </c>
-      <c r="H20" s="5">
+      <c r="H20" s="20">
         <v>1.1</v>
       </c>
-      <c r="I20" s="5">
-        <v>6</v>
-      </c>
-      <c r="J20" s="5">
-        <v>55</v>
-      </c>
-      <c r="K20" t="s" s="6">
-        <v>54</v>
-      </c>
-      <c r="L20" s="5">
-        <v>0</v>
-      </c>
-      <c r="M20" s="5">
-        <v>1010</v>
+      <c r="I20" t="s" s="9">
+        <v>26</v>
+      </c>
+      <c r="J20" t="s" s="9">
+        <v>27</v>
+      </c>
+      <c r="K20" t="s" s="9">
+        <v>28</v>
+      </c>
+      <c r="L20" t="s" s="9">
+        <v>66</v>
+      </c>
+      <c r="M20" t="s" s="21">
+        <v>67</v>
       </c>
     </row>
     <row r="21" ht="20.05" customHeight="1">
       <c r="A21" s="2"/>
-      <c r="B21" s="3"/>
-      <c r="C21" s="5">
+      <c r="B21" s="6"/>
+      <c r="C21" s="18">
         <v>16</v>
       </c>
-      <c r="D21" t="s" s="6">
-        <v>55</v>
-      </c>
-      <c r="E21" s="5">
+      <c r="D21" t="s" s="19">
+        <v>68</v>
+      </c>
+      <c r="E21" s="18">
         <v>6</v>
       </c>
-      <c r="F21" s="5">
+      <c r="F21" s="18">
         <v>4</v>
       </c>
-      <c r="G21" s="5">
+      <c r="G21" s="18">
         <v>9</v>
       </c>
-      <c r="H21" s="5">
+      <c r="H21" s="20">
         <v>1.3</v>
       </c>
-      <c r="I21" s="5">
-        <v>6</v>
-      </c>
-      <c r="J21" s="5">
-        <v>65</v>
-      </c>
-      <c r="K21" t="s" s="6">
-        <v>56</v>
-      </c>
-      <c r="L21" s="5">
-        <v>0</v>
-      </c>
-      <c r="M21" s="5">
-        <v>1010</v>
+      <c r="I21" t="s" s="9">
+        <v>26</v>
+      </c>
+      <c r="J21" t="s" s="9">
+        <v>27</v>
+      </c>
+      <c r="K21" t="s" s="9">
+        <v>28</v>
+      </c>
+      <c r="L21" t="s" s="9">
+        <v>69</v>
+      </c>
+      <c r="M21" t="s" s="21">
+        <v>70</v>
       </c>
     </row>
     <row r="22" ht="20.05" customHeight="1">
       <c r="A22" s="2"/>
-      <c r="B22" s="3"/>
-      <c r="C22" s="5">
+      <c r="B22" s="6"/>
+      <c r="C22" s="18">
         <v>17</v>
       </c>
-      <c r="D22" t="s" s="6">
-        <v>57</v>
-      </c>
-      <c r="E22" s="5">
+      <c r="D22" t="s" s="19">
+        <v>71</v>
+      </c>
+      <c r="E22" s="18">
         <v>6</v>
       </c>
-      <c r="F22" s="5">
+      <c r="F22" s="18">
         <v>3</v>
       </c>
-      <c r="G22" s="5">
+      <c r="G22" s="18">
         <v>9</v>
       </c>
-      <c r="H22" s="5">
+      <c r="H22" s="20">
         <v>1.25</v>
       </c>
-      <c r="I22" s="5">
-        <v>6</v>
-      </c>
-      <c r="J22" s="5">
-        <v>62</v>
-      </c>
-      <c r="K22" t="s" s="6">
-        <v>58</v>
-      </c>
-      <c r="L22" s="5">
-        <v>0</v>
-      </c>
-      <c r="M22" s="5">
-        <v>1010</v>
+      <c r="I22" t="s" s="9">
+        <v>26</v>
+      </c>
+      <c r="J22" t="s" s="9">
+        <v>27</v>
+      </c>
+      <c r="K22" t="s" s="9">
+        <v>28</v>
+      </c>
+      <c r="L22" t="s" s="9">
+        <v>69</v>
+      </c>
+      <c r="M22" t="s" s="21">
+        <v>72</v>
       </c>
     </row>
     <row r="23" ht="20.05" customHeight="1">
       <c r="A23" s="2"/>
-      <c r="B23" s="3"/>
-      <c r="C23" s="5">
+      <c r="B23" s="6"/>
+      <c r="C23" s="18">
         <v>18</v>
       </c>
-      <c r="D23" t="s" s="6">
-        <v>59</v>
-      </c>
-      <c r="E23" s="5">
+      <c r="D23" t="s" s="19">
+        <v>73</v>
+      </c>
+      <c r="E23" s="18">
         <v>7</v>
       </c>
-      <c r="F23" s="5">
+      <c r="F23" s="18">
         <v>8</v>
       </c>
-      <c r="G23" s="5">
+      <c r="G23" s="18">
         <v>0</v>
       </c>
-      <c r="H23" s="5">
+      <c r="H23" s="20">
         <v>3</v>
       </c>
-      <c r="I23" s="5">
-        <v>0</v>
-      </c>
-      <c r="J23" s="5">
-        <v>100</v>
-      </c>
-      <c r="K23" t="s" s="6">
-        <v>60</v>
-      </c>
-      <c r="L23" s="5">
-        <v>1</v>
-      </c>
-      <c r="M23" s="3"/>
+      <c r="I23" t="s" s="9">
+        <v>26</v>
+      </c>
+      <c r="J23" t="s" s="9">
+        <v>27</v>
+      </c>
+      <c r="K23" t="s" s="9">
+        <v>28</v>
+      </c>
+      <c r="L23" t="s" s="9">
+        <v>69</v>
+      </c>
+      <c r="M23" t="s" s="21">
+        <v>74</v>
+      </c>
     </row>
     <row r="24" ht="20.05" customHeight="1">
       <c r="A24" s="2"/>
-      <c r="B24" s="3"/>
-      <c r="C24" s="5">
+      <c r="B24" s="6"/>
+      <c r="C24" s="18">
         <v>19</v>
       </c>
-      <c r="D24" t="s" s="6">
-        <v>61</v>
-      </c>
-      <c r="E24" s="5">
+      <c r="D24" t="s" s="19">
+        <v>75</v>
+      </c>
+      <c r="E24" s="18">
         <v>8</v>
       </c>
-      <c r="F24" s="5">
+      <c r="F24" s="18">
         <v>7</v>
       </c>
-      <c r="G24" s="5">
+      <c r="G24" s="18">
         <v>0</v>
       </c>
-      <c r="H24" s="5">
+      <c r="H24" s="20">
         <v>3</v>
       </c>
-      <c r="I24" s="5">
-        <v>0</v>
-      </c>
-      <c r="J24" s="5">
-        <v>100</v>
-      </c>
-      <c r="K24" t="s" s="6">
-        <v>60</v>
-      </c>
-      <c r="L24" s="5">
-        <v>1</v>
-      </c>
-      <c r="M24" s="3"/>
+      <c r="I24" t="s" s="9">
+        <v>26</v>
+      </c>
+      <c r="J24" t="s" s="9">
+        <v>27</v>
+      </c>
+      <c r="K24" t="s" s="9">
+        <v>28</v>
+      </c>
+      <c r="L24" t="s" s="9">
+        <v>69</v>
+      </c>
+      <c r="M24" t="s" s="21">
+        <v>74</v>
+      </c>
     </row>
     <row r="25" ht="20.05" customHeight="1">
       <c r="A25" s="2"/>
-      <c r="B25" s="3"/>
-      <c r="C25" s="5">
+      <c r="B25" s="6"/>
+      <c r="C25" s="18">
         <v>20</v>
       </c>
-      <c r="D25" t="s" s="6">
-        <v>62</v>
-      </c>
-      <c r="E25" s="5">
+      <c r="D25" t="s" s="19">
+        <v>76</v>
+      </c>
+      <c r="E25" s="18">
         <v>2</v>
       </c>
-      <c r="F25" s="5">
+      <c r="F25" s="18">
         <v>3</v>
       </c>
-      <c r="G25" s="5">
+      <c r="G25" s="18">
         <v>6</v>
       </c>
-      <c r="H25" s="5">
+      <c r="H25" s="20">
         <v>1</v>
       </c>
-      <c r="I25" s="5">
-        <v>3</v>
-      </c>
-      <c r="J25" s="5">
-        <v>100</v>
-      </c>
-      <c r="K25" t="s" s="6">
-        <v>42</v>
-      </c>
-      <c r="L25" s="5">
-        <v>1</v>
-      </c>
-      <c r="M25" s="5">
-        <v>1005</v>
+      <c r="I25" t="s" s="9">
+        <v>26</v>
+      </c>
+      <c r="J25" t="s" s="9">
+        <v>27</v>
+      </c>
+      <c r="K25" t="s" s="9">
+        <v>28</v>
+      </c>
+      <c r="L25" t="s" s="9">
+        <v>77</v>
+      </c>
+      <c r="M25" t="s" s="21">
+        <v>51</v>
       </c>
     </row>
     <row r="26" ht="20.05" customHeight="1">
       <c r="A26" s="2"/>
-      <c r="B26" s="3"/>
-      <c r="C26" s="5">
+      <c r="B26" s="6"/>
+      <c r="C26" s="18">
         <v>21</v>
       </c>
-      <c r="D26" t="s" s="6">
-        <v>63</v>
-      </c>
-      <c r="E26" s="5">
+      <c r="D26" t="s" s="19">
+        <v>78</v>
+      </c>
+      <c r="E26" s="18">
         <v>3</v>
       </c>
-      <c r="F26" s="5">
+      <c r="F26" s="18">
         <v>4</v>
       </c>
-      <c r="G26" s="5">
+      <c r="G26" s="18">
         <v>4</v>
       </c>
-      <c r="H26" s="5">
+      <c r="H26" s="20">
         <v>2</v>
       </c>
-      <c r="I26" s="5">
-        <v>0</v>
-      </c>
-      <c r="J26" s="5">
-        <v>0</v>
-      </c>
-      <c r="K26" t="s" s="6">
-        <v>34</v>
-      </c>
-      <c r="L26" s="5">
-        <v>0</v>
-      </c>
-      <c r="M26" s="5">
-        <v>555</v>
+      <c r="I26" t="s" s="9">
+        <v>26</v>
+      </c>
+      <c r="J26" t="s" s="9">
+        <v>27</v>
+      </c>
+      <c r="K26" t="s" s="9">
+        <v>28</v>
+      </c>
+      <c r="L26" t="s" s="9">
+        <v>79</v>
+      </c>
+      <c r="M26" t="s" s="21">
+        <v>40</v>
       </c>
     </row>
     <row r="27" ht="20.05" customHeight="1">
       <c r="A27" s="2"/>
-      <c r="B27" s="3"/>
-      <c r="C27" s="5">
+      <c r="B27" s="6"/>
+      <c r="C27" s="18">
         <v>22</v>
       </c>
-      <c r="D27" t="s" s="6">
-        <v>64</v>
-      </c>
-      <c r="E27" s="5">
+      <c r="D27" t="s" s="19">
+        <v>80</v>
+      </c>
+      <c r="E27" s="18">
         <v>4</v>
       </c>
-      <c r="F27" s="5">
+      <c r="F27" s="18">
         <v>1</v>
       </c>
-      <c r="G27" s="5">
+      <c r="G27" s="18">
         <v>3</v>
       </c>
-      <c r="H27" s="5">
+      <c r="H27" s="20">
         <v>2.5</v>
       </c>
-      <c r="I27" s="5">
-        <v>0</v>
-      </c>
-      <c r="J27" s="5">
-        <v>100</v>
-      </c>
-      <c r="K27" t="s" s="6">
-        <v>40</v>
-      </c>
-      <c r="L27" s="5">
-        <v>1</v>
-      </c>
-      <c r="M27" s="5">
-        <v>1013</v>
+      <c r="I27" t="s" s="9">
+        <v>26</v>
+      </c>
+      <c r="J27" t="s" s="9">
+        <v>27</v>
+      </c>
+      <c r="K27" t="s" s="9">
+        <v>28</v>
+      </c>
+      <c r="L27" t="s" s="9">
+        <v>29</v>
+      </c>
+      <c r="M27" t="s" s="21">
+        <v>48</v>
       </c>
     </row>
     <row r="28" ht="20.05" customHeight="1">
       <c r="A28" s="2"/>
-      <c r="B28" s="3"/>
-      <c r="C28" s="5">
+      <c r="B28" s="6"/>
+      <c r="C28" s="18">
         <v>23</v>
       </c>
-      <c r="D28" t="s" s="6">
-        <v>65</v>
-      </c>
-      <c r="E28" s="5">
+      <c r="D28" t="s" s="19">
+        <v>81</v>
+      </c>
+      <c r="E28" s="18">
         <v>1</v>
       </c>
-      <c r="F28" s="5">
+      <c r="F28" s="18">
         <v>5</v>
       </c>
-      <c r="G28" s="5">
+      <c r="G28" s="18">
         <v>8</v>
       </c>
-      <c r="H28" s="5">
+      <c r="H28" s="20">
         <v>1.3</v>
       </c>
-      <c r="I28" s="5">
-        <v>5</v>
-      </c>
-      <c r="J28" s="5">
-        <v>50</v>
-      </c>
-      <c r="K28" t="s" s="6">
-        <v>36</v>
-      </c>
-      <c r="L28" s="5">
-        <v>0</v>
-      </c>
-      <c r="M28" s="5">
-        <v>1006</v>
+      <c r="I28" t="s" s="9">
+        <v>26</v>
+      </c>
+      <c r="J28" t="s" s="9">
+        <v>27</v>
+      </c>
+      <c r="K28" t="s" s="9">
+        <v>28</v>
+      </c>
+      <c r="L28" t="s" s="9">
+        <v>29</v>
+      </c>
+      <c r="M28" t="s" s="21">
+        <v>43</v>
       </c>
     </row>
     <row r="29" ht="20.05" customHeight="1">
       <c r="A29" s="2"/>
-      <c r="B29" s="3"/>
-      <c r="C29" s="5">
+      <c r="B29" s="6"/>
+      <c r="C29" s="18">
         <v>24</v>
       </c>
-      <c r="D29" t="s" s="6">
-        <v>66</v>
-      </c>
-      <c r="E29" s="5">
+      <c r="D29" t="s" s="19">
+        <v>82</v>
+      </c>
+      <c r="E29" s="18">
         <v>2</v>
       </c>
-      <c r="F29" s="5">
+      <c r="F29" s="18">
         <v>5</v>
       </c>
-      <c r="G29" s="5">
+      <c r="G29" s="18">
         <v>8</v>
       </c>
-      <c r="H29" s="5">
+      <c r="H29" s="20">
         <v>1.2</v>
       </c>
-      <c r="I29" s="5">
-        <v>5</v>
-      </c>
-      <c r="J29" s="5">
-        <v>45</v>
-      </c>
-      <c r="K29" t="s" s="6">
-        <v>46</v>
-      </c>
-      <c r="L29" s="5">
-        <v>0</v>
-      </c>
-      <c r="M29" s="5">
-        <v>1007</v>
+      <c r="I29" t="s" s="9">
+        <v>26</v>
+      </c>
+      <c r="J29" t="s" s="9">
+        <v>27</v>
+      </c>
+      <c r="K29" t="s" s="9">
+        <v>28</v>
+      </c>
+      <c r="L29" t="s" s="9">
+        <v>39</v>
+      </c>
+      <c r="M29" t="s" s="21">
+        <v>55</v>
       </c>
     </row>
     <row r="30" ht="20.05" customHeight="1">
       <c r="A30" s="2"/>
-      <c r="B30" s="3"/>
-      <c r="C30" s="5">
+      <c r="B30" s="6"/>
+      <c r="C30" s="18">
         <v>25</v>
       </c>
-      <c r="D30" t="s" s="6">
-        <v>67</v>
-      </c>
-      <c r="E30" s="5">
+      <c r="D30" t="s" s="19">
+        <v>83</v>
+      </c>
+      <c r="E30" s="18">
         <v>3</v>
       </c>
-      <c r="F30" s="5">
+      <c r="F30" s="18">
         <v>5</v>
       </c>
-      <c r="G30" s="5">
+      <c r="G30" s="18">
         <v>8</v>
       </c>
-      <c r="H30" s="5">
+      <c r="H30" s="20">
         <v>1.4</v>
       </c>
-      <c r="I30" s="5">
-        <v>5</v>
-      </c>
-      <c r="J30" s="5">
-        <v>48</v>
-      </c>
-      <c r="K30" t="s" s="6">
-        <v>48</v>
-      </c>
-      <c r="L30" s="5">
-        <v>0</v>
-      </c>
-      <c r="M30" s="5">
-        <v>1008</v>
+      <c r="I30" t="s" s="9">
+        <v>26</v>
+      </c>
+      <c r="J30" t="s" s="9">
+        <v>27</v>
+      </c>
+      <c r="K30" t="s" s="9">
+        <v>28</v>
+      </c>
+      <c r="L30" t="s" s="9">
+        <v>69</v>
+      </c>
+      <c r="M30" t="s" s="21">
+        <v>58</v>
       </c>
     </row>
     <row r="31" ht="20.05" customHeight="1">
       <c r="A31" s="2"/>
-      <c r="B31" s="3"/>
-      <c r="C31" s="5">
-        <v>26</v>
-      </c>
-      <c r="D31" t="s" s="6">
-        <v>68</v>
-      </c>
-      <c r="E31" s="5">
+      <c r="B31" s="6"/>
+      <c r="C31" s="18">
+        <v>26</v>
+      </c>
+      <c r="D31" t="s" s="19">
+        <v>84</v>
+      </c>
+      <c r="E31" s="18">
         <v>4</v>
       </c>
-      <c r="F31" s="5">
+      <c r="F31" s="18">
         <v>5</v>
       </c>
-      <c r="G31" s="5">
+      <c r="G31" s="18">
         <v>8</v>
       </c>
-      <c r="H31" s="5">
+      <c r="H31" s="20">
         <v>1.6</v>
       </c>
-      <c r="I31" s="5">
-        <v>5</v>
-      </c>
-      <c r="J31" s="5">
-        <v>52</v>
-      </c>
-      <c r="K31" t="s" s="6">
-        <v>50</v>
-      </c>
-      <c r="L31" s="5">
-        <v>0</v>
-      </c>
-      <c r="M31" s="5">
-        <v>1009</v>
+      <c r="I31" t="s" s="9">
+        <v>26</v>
+      </c>
+      <c r="J31" t="s" s="9">
+        <v>27</v>
+      </c>
+      <c r="K31" t="s" s="9">
+        <v>28</v>
+      </c>
+      <c r="L31" t="s" s="9">
+        <v>69</v>
+      </c>
+      <c r="M31" t="s" s="21">
+        <v>61</v>
       </c>
     </row>
     <row r="32" ht="20.05" customHeight="1">
       <c r="A32" s="2"/>
-      <c r="B32" s="3"/>
-      <c r="C32" s="5">
-        <v>27</v>
-      </c>
-      <c r="D32" t="s" s="6">
-        <v>69</v>
-      </c>
-      <c r="E32" s="5">
+      <c r="B32" s="6"/>
+      <c r="C32" s="18">
+        <v>27</v>
+      </c>
+      <c r="D32" t="s" s="19">
+        <v>85</v>
+      </c>
+      <c r="E32" s="18">
         <v>1</v>
       </c>
-      <c r="F32" s="5">
+      <c r="F32" s="18">
         <v>6</v>
       </c>
-      <c r="G32" s="5">
+      <c r="G32" s="18">
         <v>9</v>
       </c>
-      <c r="H32" s="5">
+      <c r="H32" s="20">
         <v>1.2</v>
       </c>
-      <c r="I32" s="5">
-        <v>6</v>
-      </c>
-      <c r="J32" s="5">
-        <v>60</v>
-      </c>
-      <c r="K32" t="s" s="6">
-        <v>52</v>
-      </c>
-      <c r="L32" s="5">
-        <v>0</v>
-      </c>
-      <c r="M32" s="5">
-        <v>1010</v>
+      <c r="I32" t="s" s="9">
+        <v>26</v>
+      </c>
+      <c r="J32" t="s" s="9">
+        <v>27</v>
+      </c>
+      <c r="K32" t="s" s="9">
+        <v>28</v>
+      </c>
+      <c r="L32" t="s" s="9">
+        <v>77</v>
+      </c>
+      <c r="M32" t="s" s="21">
+        <v>64</v>
       </c>
     </row>
     <row r="33" ht="20.05" customHeight="1">
       <c r="A33" s="2"/>
-      <c r="B33" s="3"/>
-      <c r="C33" s="5">
-        <v>28</v>
-      </c>
-      <c r="D33" t="s" s="6">
-        <v>70</v>
-      </c>
-      <c r="E33" s="5">
+      <c r="B33" s="6"/>
+      <c r="C33" s="18">
+        <v>28</v>
+      </c>
+      <c r="D33" t="s" s="19">
+        <v>86</v>
+      </c>
+      <c r="E33" s="18">
         <v>2</v>
       </c>
-      <c r="F33" s="5">
+      <c r="F33" s="18">
         <v>6</v>
       </c>
-      <c r="G33" s="5">
+      <c r="G33" s="18">
         <v>9</v>
       </c>
-      <c r="H33" s="5">
+      <c r="H33" s="20">
         <v>1.1</v>
       </c>
-      <c r="I33" s="5">
-        <v>6</v>
-      </c>
-      <c r="J33" s="5">
-        <v>55</v>
-      </c>
-      <c r="K33" t="s" s="6">
-        <v>54</v>
-      </c>
-      <c r="L33" s="5">
-        <v>0</v>
-      </c>
-      <c r="M33" s="5">
-        <v>1010</v>
+      <c r="I33" t="s" s="9">
+        <v>26</v>
+      </c>
+      <c r="J33" t="s" s="9">
+        <v>27</v>
+      </c>
+      <c r="K33" t="s" s="9">
+        <v>28</v>
+      </c>
+      <c r="L33" t="s" s="9">
+        <v>79</v>
+      </c>
+      <c r="M33" t="s" s="21">
+        <v>67</v>
       </c>
     </row>
     <row r="34" ht="20.05" customHeight="1">
       <c r="A34" s="2"/>
-      <c r="B34" s="3"/>
-      <c r="C34" s="5">
+      <c r="B34" s="6"/>
+      <c r="C34" s="18">
         <v>29</v>
       </c>
-      <c r="D34" t="s" s="6">
-        <v>71</v>
-      </c>
-      <c r="E34" s="5">
+      <c r="D34" t="s" s="19">
+        <v>87</v>
+      </c>
+      <c r="E34" s="18">
         <v>4</v>
       </c>
-      <c r="F34" s="5">
+      <c r="F34" s="18">
         <v>6</v>
       </c>
-      <c r="G34" s="5">
+      <c r="G34" s="18">
         <v>9</v>
       </c>
-      <c r="H34" s="5">
+      <c r="H34" s="20">
         <v>1.3</v>
       </c>
-      <c r="I34" s="5">
-        <v>6</v>
-      </c>
-      <c r="J34" s="5">
-        <v>65</v>
-      </c>
-      <c r="K34" t="s" s="6">
-        <v>56</v>
-      </c>
-      <c r="L34" s="5">
-        <v>0</v>
-      </c>
-      <c r="M34" s="5">
-        <v>1010</v>
+      <c r="I34" t="s" s="9">
+        <v>26</v>
+      </c>
+      <c r="J34" t="s" s="9">
+        <v>27</v>
+      </c>
+      <c r="K34" t="s" s="9">
+        <v>28</v>
+      </c>
+      <c r="L34" t="s" s="9">
+        <v>29</v>
+      </c>
+      <c r="M34" t="s" s="21">
+        <v>70</v>
       </c>
     </row>
     <row r="35" ht="20.05" customHeight="1">
       <c r="A35" s="2"/>
-      <c r="B35" s="3"/>
-      <c r="C35" s="5">
+      <c r="B35" s="6"/>
+      <c r="C35" s="18">
         <v>30</v>
       </c>
-      <c r="D35" t="s" s="6">
+      <c r="D35" t="s" s="19">
+        <v>88</v>
+      </c>
+      <c r="E35" s="18">
+        <v>3</v>
+      </c>
+      <c r="F35" s="18">
+        <v>6</v>
+      </c>
+      <c r="G35" s="18">
+        <v>9</v>
+      </c>
+      <c r="H35" s="20">
+        <v>1.25</v>
+      </c>
+      <c r="I35" t="s" s="9">
+        <v>26</v>
+      </c>
+      <c r="J35" t="s" s="9">
+        <v>27</v>
+      </c>
+      <c r="K35" t="s" s="9">
+        <v>28</v>
+      </c>
+      <c r="L35" t="s" s="9">
+        <v>29</v>
+      </c>
+      <c r="M35" t="s" s="21">
         <v>72</v>
-      </c>
-      <c r="E35" s="5">
-        <v>3</v>
-      </c>
-      <c r="F35" s="5">
-        <v>6</v>
-      </c>
-      <c r="G35" s="5">
-        <v>9</v>
-      </c>
-      <c r="H35" s="5">
-        <v>1.25</v>
-      </c>
-      <c r="I35" s="5">
-        <v>6</v>
-      </c>
-      <c r="J35" s="5">
-        <v>62</v>
-      </c>
-      <c r="K35" t="s" s="6">
-        <v>58</v>
-      </c>
-      <c r="L35" s="5">
-        <v>0</v>
-      </c>
-      <c r="M35" s="5">
-        <v>1010</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/Skill/ElementReactionConfig.xlsx
+++ b/Unity/Assets/Config/Excel/Skill/ElementReactionConfig.xlsx
@@ -64,7 +64,7 @@
     <t>Intensity</t>
   </si>
   <si>
-    <t>DaceyPerSecond</t>
+    <t>DecayPerSecond</t>
   </si>
   <si>
     <t>Duration</t>
